--- a/data/trans_orig/IP16A98-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>22785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>49296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58572</t>
+          <t>59122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>31664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61485</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71526</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57490</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65120</t>
+          <t>65215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78701</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31573</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>119744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132893</t>
+          <t>132808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122982</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138009</t>
+          <t>138067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247444</t>
+          <t>247471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266839</t>
+          <t>267594</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42391</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>26624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26101</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34943</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57069</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69732</t>
+          <t>69940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>51885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>47630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57853</t>
+          <t>57275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111758</t>
+          <t>112221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104959</t>
+          <t>104254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193954</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213497</t>
+          <t>212810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19163</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34338</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46249</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21550</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40290</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>48479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95699</t>
+          <t>95688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>57379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>73982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36418</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52749</t>
+          <t>53073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100064</t>
+          <t>99247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20721</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55769</t>
+          <t>55772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>49549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85107</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158059</t>
+          <t>158100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136646</t>
+          <t>135766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157541</t>
+          <t>158238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274809</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313051</t>
+          <t>310367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A98-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A98-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10682</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4857</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8661</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8820</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2922</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10885</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27732</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23040</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30798</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26589</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22785</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29268</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29421</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27732</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22837</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30800</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33722</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33722</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33722</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>33722</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>33722</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>33722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9038</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7213</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4090</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11682</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8656</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35545</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38341</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31920</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27451</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35043</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27364</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35236</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35545</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31664</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38289</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61762</t>
+          <t>61954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71935</t>
+          <t>72129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>39133</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>39133</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>39133</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6682</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4991</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7174</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31459</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28077</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33551</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31067</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27973</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27820</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32366</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31459</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27585</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33529</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>58323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>65286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34759</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34759</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34759</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>34759</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34759</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9410</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14575</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3507</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7714</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9410</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5625</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15135</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36345</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>40298</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>37566</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33359</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39770</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33538</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>39774</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>36345</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30620</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>40130</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>78783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45755</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45755</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45755</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41073</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41073</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41073</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>45755</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>45755</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>45755</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16896</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31398</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11808</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24872</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24464</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16488</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31501</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51700</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131080</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137659</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>127143</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119744</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>132808</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>120152</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>132809</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>83,08%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>131080</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123054</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>138067</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>79,62%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>366</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247471</t>
+          <t>247392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267594</t>
+          <t>267321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>154555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>144616</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>154555</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9045</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5728</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9944</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10332</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1682</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8477</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15131</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22057</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18631</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21713</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14027</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21507</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15699</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22494</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>32555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>10180</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15070</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>9930</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14634</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15124</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6056</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14994</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30967</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26077</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35422</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32769</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28065</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36710</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27575</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36993</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30967</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26153</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35091</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57222</t>
+          <t>56797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69940</t>
+          <t>70152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8730</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1881</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5187</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22691</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19076</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25498</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25734</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22428</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27090</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22561</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27086</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22691</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18367</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25273</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>43688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51885</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4129</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8474</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1759</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8205</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5187</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9259</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24959</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20786</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27896</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28659</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24314</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31188</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31029</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24959</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20887</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27923</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57275</t>
+          <t>57623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33081</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15240</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29441</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29092</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19022</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>33523</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58056</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98231</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90195</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>105090</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>105793</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98020</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112221</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98369</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>112688</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>98231</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>89753</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>104254</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192681</t>
+          <t>193591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>212810</t>
+          <t>213308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2272</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11238</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6561</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3426</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10287</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40780</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34456</t>
+          <t>33162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>43691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4376</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12474</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10427</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4209</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24687</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>20224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48609</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43984</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52082</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33815</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19555</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40033</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>79233</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95688</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19898</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10778</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19692</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43277</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32457</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48392</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>66293</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57379</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73982</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47452</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>34833</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53073</t>
+          <t>44386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>113746</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99247</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123641</t>
+          <t>90456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4732</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12646</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8930</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23543</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18871</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26785</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>25584</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21631</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28208</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51104</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55772</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21832</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19615</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49092</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>46288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>71920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134659</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122194</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143120</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>128623</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>158100</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>148685</t>
+          <t>115180</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135766</t>
+          <t>107536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158238</t>
+          <t>122620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>293657</t>
+          <t>249839</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273564</t>
+          <t>236024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310367</t>
+          <t>261656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
